--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_1_9.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_1_9.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>269011.4271123341</v>
+        <v>279275.7438591642</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4964010.941928674</v>
+        <v>4921297.203522783</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22285259.10284261</v>
+        <v>22243395.367831</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4042763.973696852</v>
+        <v>4061563.731276019</v>
       </c>
     </row>
     <row r="11">
@@ -1846,16 +1846,16 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4.006138603635352</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1964,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.006138603635353</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>4.006138603635353</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -2040,10 +2040,10 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
     </row>
     <row r="20">
@@ -2074,10 +2074,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2116,19 +2116,19 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T20" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="V20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -2147,28 +2147,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="G21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -2274,13 +2274,13 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T22" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2289,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y22" t="n">
-        <v>40</v>
+        <v>0.790450447682262</v>
       </c>
     </row>
     <row r="23">
@@ -2308,25 +2308,25 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="I23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>35.23199999999998</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="24">
@@ -2387,19 +2387,19 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="D24" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="G24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2432,10 +2432,10 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.790450447682262</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -2481,13 +2481,13 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>9.137025436486079</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2523,16 +2523,16 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="26">
@@ -2590,25 +2590,25 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U26" t="n">
-        <v>35.23199999999998</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2678,19 +2678,19 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X27" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="28">
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -2721,13 +2721,13 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>22.653131001028</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2751,13 +2751,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="29">
@@ -2782,16 +2782,16 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="D29" t="n">
-        <v>25.24130078545516</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2833,22 +2833,22 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="X29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2906,10 +2906,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -2918,16 +2918,16 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
     </row>
     <row r="31">
@@ -2937,16 +2937,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="C31" t="n">
-        <v>40</v>
+        <v>0.790450447682262</v>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>9.137025436486079</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2988,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3000,13 +3000,13 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="32">
@@ -3019,16 +3019,16 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F32" t="n">
-        <v>35.23199999999997</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -3064,10 +3064,10 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -3098,28 +3098,28 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>34.48540867374211</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -3158,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -3189,10 +3189,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>9.137025436486079</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3225,25 +3225,25 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>0.790450447682262</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="35">
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="C35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3301,19 +3301,19 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>35.23199999999998</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -3332,13 +3332,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3383,25 +3383,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="37">
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="D37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>0.7904504476822691</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3471,16 +3471,16 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="38">
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3538,19 +3538,19 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>40</v>
+        <v>26.92232807701203</v>
       </c>
       <c r="T38" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U38" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -3578,13 +3578,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3623,22 +3623,22 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y39" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -3690,28 +3690,28 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="S40" t="n">
-        <v>9.137025436486075</v>
+        <v>42.20118209180435</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3730,13 +3730,13 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3787,16 +3787,16 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>40</v>
+        <v>24.87477961344436</v>
       </c>
       <c r="X41" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Y41" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3809,10 +3809,10 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>40</v>
+        <v>34.11888750173132</v>
       </c>
       <c r="D42" t="n">
-        <v>35.23199999999997</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -3824,13 +3824,13 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3863,10 +3863,10 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -3875,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="43">
@@ -3927,31 +3927,31 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="S43" t="n">
-        <v>9.137025436486075</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="T43" t="n">
-        <v>40</v>
+        <v>7.256111626157765</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>9.552339224073879</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>4.958101428732459</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4.866676096605165</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.866676096605165</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>9.187556743123771</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>9.187556743123771</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>13.69036920633789</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>4.866676096605165</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>9.369488559819288</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>13.87230102303341</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>9.00470607886918</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.410468283527761</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4.866676096605165</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>9.369488559819288</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>13.69036920633789</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>9.00470607886918</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>9.00470607886918</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>9.00470607886918</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>9.00470607886918</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>9.00470607886918</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>4.410468283527761</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C20" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D20" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K20" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L20" t="n">
-        <v>80.80000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M20" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="N20" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O20" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R20" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="S20" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="T20" t="n">
-        <v>119.5959595959596</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="U20" t="n">
-        <v>119.5959595959596</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="V20" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="W20" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="X20" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="Y20" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="C21" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="D21" t="n">
-        <v>160</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="E21" t="n">
-        <v>160</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="F21" t="n">
-        <v>119.5959595959596</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G21" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H21" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K21" t="n">
-        <v>42.8</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="L21" t="n">
-        <v>42.8</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="M21" t="n">
-        <v>42.8</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="N21" t="n">
-        <v>80.80000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="O21" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P21" t="n">
-        <v>160</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="Q21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="W21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="X21" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="Y21" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C22" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D22" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E22" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F22" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G22" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L22" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M22" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N22" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O22" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P22" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q22" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R22" t="n">
-        <v>133.6414398348344</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="S22" t="n">
-        <v>133.6414398348344</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="T22" t="n">
-        <v>124.4121212121212</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="U22" t="n">
-        <v>124.4121212121212</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="V22" t="n">
-        <v>124.4121212121212</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="W22" t="n">
-        <v>84.00808080808082</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="X22" t="n">
-        <v>84.00808080808082</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="Y22" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>124.4121212121212</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="C23" t="n">
-        <v>84.00808080808082</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="D23" t="n">
-        <v>43.60404040404041</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="E23" t="n">
-        <v>43.60404040404041</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="F23" t="n">
-        <v>43.60404040404041</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="G23" t="n">
-        <v>43.60404040404041</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="H23" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K23" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L23" t="n">
-        <v>82.40000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M23" t="n">
-        <v>120.4</v>
+        <v>134.6031257566472</v>
       </c>
       <c r="N23" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="O23" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P23" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q23" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R23" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S23" t="n">
-        <v>124.4121212121212</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="T23" t="n">
-        <v>124.4121212121212</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="U23" t="n">
-        <v>124.4121212121212</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="V23" t="n">
-        <v>124.4121212121212</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="W23" t="n">
-        <v>124.4121212121212</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="X23" t="n">
-        <v>124.4121212121212</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="Y23" t="n">
-        <v>124.4121212121212</v>
+        <v>92.68647758675968</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="C24" t="n">
-        <v>160</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="D24" t="n">
-        <v>124.4121212121212</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="E24" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="F24" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L24" t="n">
-        <v>3.2</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="N24" t="n">
-        <v>41.20000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="O24" t="n">
-        <v>80.80000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P24" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q24" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R24" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="S24" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="T24" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="U24" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="V24" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="W24" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="X24" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="Y24" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>93.23739943079403</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="C25" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D25" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E25" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F25" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G25" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H25" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I25" t="n">
-        <v>12.42931862271321</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L25" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M25" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N25" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="T25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="U25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="V25" t="n">
-        <v>93.23739943079403</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="W25" t="n">
-        <v>93.23739943079403</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="X25" t="n">
-        <v>93.23739943079403</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="Y25" t="n">
-        <v>93.23739943079403</v>
+        <v>4.329008585976936</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K26" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L26" t="n">
-        <v>82.40000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="M26" t="n">
-        <v>122</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="N26" t="n">
-        <v>160</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O26" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P26" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q26" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R26" t="n">
-        <v>160</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="S26" t="n">
-        <v>160</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="T26" t="n">
-        <v>160</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="U26" t="n">
-        <v>124.4121212121212</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="V26" t="n">
-        <v>84.00808080808082</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="W26" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="X26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="C27" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="D27" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="E27" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="G27" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K27" t="n">
-        <v>42.8</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L27" t="n">
-        <v>82.40000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M27" t="n">
-        <v>82.40000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="N27" t="n">
-        <v>120.4</v>
+        <v>134.6031257566472</v>
       </c>
       <c r="O27" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P27" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q27" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R27" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S27" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T27" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U27" t="n">
-        <v>124.4121212121212</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V27" t="n">
-        <v>84.00808080808082</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="W27" t="n">
-        <v>43.60404040404041</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="X27" t="n">
-        <v>3.2</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="Y27" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>43.60404040404041</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="C28" t="n">
-        <v>3.2</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="D28" t="n">
-        <v>3.2</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="E28" t="n">
-        <v>3.2</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="F28" t="n">
-        <v>3.2</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="G28" t="n">
-        <v>3.2</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="H28" t="n">
-        <v>3.2</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>26.02500997809875</v>
       </c>
       <c r="K28" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L28" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M28" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N28" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O28" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P28" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q28" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R28" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S28" t="n">
-        <v>124.4121212121212</v>
+        <v>138.062864280609</v>
       </c>
       <c r="T28" t="n">
-        <v>84.00808080808082</v>
+        <v>138.062864280609</v>
       </c>
       <c r="U28" t="n">
-        <v>43.60404040404041</v>
+        <v>138.062864280609</v>
       </c>
       <c r="V28" t="n">
-        <v>43.60404040404041</v>
+        <v>138.062864280609</v>
       </c>
       <c r="W28" t="n">
-        <v>43.60404040404041</v>
+        <v>138.062864280609</v>
       </c>
       <c r="X28" t="n">
-        <v>43.60404040404041</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Y28" t="n">
-        <v>43.60404040404041</v>
+        <v>93.48491238239833</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>69.10030382369209</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="C29" t="n">
-        <v>69.10030382369209</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D29" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E29" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K29" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L29" t="n">
-        <v>3.2</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M29" t="n">
-        <v>42.8</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="N29" t="n">
-        <v>82.40000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O29" t="n">
-        <v>122</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P29" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q29" t="n">
-        <v>149.9083846317729</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R29" t="n">
-        <v>149.9083846317729</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S29" t="n">
-        <v>149.9083846317729</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T29" t="n">
-        <v>149.9083846317729</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="U29" t="n">
-        <v>149.9083846317729</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="V29" t="n">
-        <v>149.9083846317729</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="W29" t="n">
-        <v>149.9083846317729</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="X29" t="n">
-        <v>109.5043442277325</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="Y29" t="n">
-        <v>69.10030382369209</v>
+        <v>48.10852568854899</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="C30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K30" t="n">
-        <v>42.8</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="L30" t="n">
-        <v>80.80000000000001</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="M30" t="n">
-        <v>120.4</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="N30" t="n">
-        <v>120.4</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="O30" t="n">
-        <v>120.4</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="P30" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="Q30" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R30" t="n">
-        <v>124.4121212121212</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S30" t="n">
-        <v>124.4121212121212</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="T30" t="n">
-        <v>124.4121212121212</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="U30" t="n">
-        <v>124.4121212121212</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="V30" t="n">
-        <v>84.00808080808082</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="W30" t="n">
-        <v>43.60404040404041</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="X30" t="n">
-        <v>3.2</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="Y30" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>93.23739943079403</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="C31" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D31" t="n">
-        <v>12.42931862271321</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L31" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M31" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N31" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S31" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="T31" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="U31" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="V31" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="W31" t="n">
-        <v>93.23739943079403</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="X31" t="n">
-        <v>93.23739943079403</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="Y31" t="n">
-        <v>93.23739943079403</v>
+        <v>48.90696048418764</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>119.5959595959596</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="C32" t="n">
-        <v>79.19191919191917</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="D32" t="n">
-        <v>79.19191919191917</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="E32" t="n">
-        <v>38.78787878787876</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="F32" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G32" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H32" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K32" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L32" t="n">
-        <v>41.20000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="M32" t="n">
-        <v>80.80000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="N32" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O32" t="n">
-        <v>160</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P32" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q32" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R32" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="S32" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="T32" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="U32" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="V32" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="W32" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="X32" t="n">
-        <v>119.5959595959596</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="Y32" t="n">
-        <v>119.5959595959596</v>
+        <v>87.37278572049297</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="C33" t="n">
-        <v>79.19191919191917</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="D33" t="n">
-        <v>79.19191919191917</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="E33" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F33" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G33" t="n">
-        <v>44.35817305682612</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H33" t="n">
-        <v>3.954132652785714</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I33" t="n">
-        <v>3.954132652785714</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K33" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L33" t="n">
-        <v>41.20000000000001</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="M33" t="n">
-        <v>80.80000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="N33" t="n">
-        <v>120.4</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="O33" t="n">
-        <v>160</v>
+        <v>134.6031257566472</v>
       </c>
       <c r="P33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R33" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="S33" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="T33" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="U33" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="V33" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="W33" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="X33" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="Y33" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C34" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D34" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E34" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F34" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G34" t="n">
-        <v>12.42931862271321</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H34" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I34" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J34" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K34" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L34" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M34" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N34" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O34" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P34" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q34" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R34" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S34" t="n">
-        <v>133.6414398348344</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="T34" t="n">
-        <v>133.6414398348344</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="U34" t="n">
-        <v>133.6414398348344</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="V34" t="n">
-        <v>93.23739943079403</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="W34" t="n">
-        <v>93.23739943079403</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="X34" t="n">
-        <v>93.23739943079403</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="Y34" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K35" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L35" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M35" t="n">
-        <v>41.20000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="N35" t="n">
-        <v>80.80000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="O35" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P35" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q35" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R35" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S35" t="n">
-        <v>84.00808080808082</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="T35" t="n">
-        <v>84.00808080808082</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="U35" t="n">
-        <v>84.00808080808082</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="V35" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="W35" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="X35" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="Y35" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="C36" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="D36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K36" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L36" t="n">
-        <v>3.2</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>134.6031257566472</v>
       </c>
       <c r="N36" t="n">
-        <v>42.8</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="O36" t="n">
-        <v>82.40000000000001</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P36" t="n">
-        <v>122</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q36" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R36" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S36" t="n">
-        <v>124.4121212121212</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T36" t="n">
-        <v>124.4121212121212</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U36" t="n">
-        <v>84.00808080808082</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V36" t="n">
-        <v>43.60404040404041</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="W36" t="n">
-        <v>3.2</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="X36" t="n">
-        <v>3.2</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.2</v>
+        <v>87.37278572049297</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>84.00808080808082</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="C37" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="D37" t="n">
-        <v>43.60404040404041</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="E37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K37" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L37" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M37" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N37" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O37" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P37" t="n">
-        <v>133.6414398348344</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="Q37" t="n">
-        <v>133.6414398348344</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="R37" t="n">
-        <v>133.6414398348344</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="S37" t="n">
-        <v>133.6414398348344</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="T37" t="n">
-        <v>133.6414398348344</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="U37" t="n">
-        <v>133.6414398348344</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="V37" t="n">
-        <v>93.23739943079403</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="W37" t="n">
-        <v>93.23739943079403</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="X37" t="n">
-        <v>84.00808080808082</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="Y37" t="n">
-        <v>84.00808080808082</v>
+        <v>92.68647758675968</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="C38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="D38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="E38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="F38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="G38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="H38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K38" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L38" t="n">
-        <v>42.8</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M38" t="n">
-        <v>82.40000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="N38" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O38" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P38" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q38" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R38" t="n">
-        <v>124.4121212121212</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S38" t="n">
-        <v>84.00808080808082</v>
+        <v>149.3344187320537</v>
       </c>
       <c r="T38" t="n">
-        <v>43.60404040404041</v>
+        <v>104.756466833843</v>
       </c>
       <c r="U38" t="n">
-        <v>3.2</v>
+        <v>60.17851493563234</v>
       </c>
       <c r="V38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="W38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="X38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.2</v>
+        <v>15.60056303742164</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>43.60404040404041</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="C39" t="n">
-        <v>43.60404040404041</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="D39" t="n">
-        <v>43.60404040404041</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="E39" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F39" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L39" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M39" t="n">
-        <v>41.20000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="N39" t="n">
-        <v>80.80000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="O39" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P39" t="n">
-        <v>160</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="Q39" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R39" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S39" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T39" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="U39" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="V39" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="W39" t="n">
-        <v>79.19191919191917</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="X39" t="n">
-        <v>79.19191919191917</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="Y39" t="n">
-        <v>43.60404040404041</v>
+        <v>42.79483382228227</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C40" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D40" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E40" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F40" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G40" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H40" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I40" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J40" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K40" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L40" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M40" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N40" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O40" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P40" t="n">
-        <v>133.6414398348344</v>
+        <v>135.3139342451479</v>
       </c>
       <c r="Q40" t="n">
-        <v>133.6414398348344</v>
+        <v>90.73598234693722</v>
       </c>
       <c r="R40" t="n">
-        <v>133.6414398348344</v>
+        <v>46.15803044872652</v>
       </c>
       <c r="S40" t="n">
-        <v>124.4121212121212</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="T40" t="n">
-        <v>124.4121212121212</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="U40" t="n">
-        <v>84.00808080808082</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="V40" t="n">
-        <v>84.00808080808082</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="W40" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="X40" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="Y40" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.2</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="C41" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="D41" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="E41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K41" t="n">
-        <v>41.20000000000001</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L41" t="n">
-        <v>80.80000000000001</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="M41" t="n">
-        <v>80.80000000000001</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="N41" t="n">
-        <v>80.80000000000001</v>
+        <v>120.7308247336138</v>
       </c>
       <c r="O41" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="P41" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q41" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="R41" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="S41" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="T41" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="U41" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="V41" t="n">
-        <v>119.5959595959596</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="W41" t="n">
-        <v>79.19191919191917</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="X41" t="n">
-        <v>38.78787878787876</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="Y41" t="n">
-        <v>3.2</v>
+        <v>83.13413836268582</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>79.19191919191917</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="C42" t="n">
-        <v>38.78787878787876</v>
+        <v>83.88827101547153</v>
       </c>
       <c r="D42" t="n">
-        <v>3.2</v>
+        <v>43.90455691260225</v>
       </c>
       <c r="E42" t="n">
-        <v>3.2</v>
+        <v>43.90455691260225</v>
       </c>
       <c r="F42" t="n">
-        <v>3.2</v>
+        <v>43.90455691260225</v>
       </c>
       <c r="G42" t="n">
-        <v>3.2</v>
+        <v>43.90455691260225</v>
       </c>
       <c r="H42" t="n">
-        <v>3.2</v>
+        <v>3.920842809732961</v>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>3.920842809732961</v>
       </c>
       <c r="J42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K42" t="n">
-        <v>42.8</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="L42" t="n">
-        <v>80.80000000000001</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="M42" t="n">
-        <v>80.80000000000001</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="N42" t="n">
-        <v>80.80000000000001</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="O42" t="n">
-        <v>80.80000000000001</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="P42" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="Q42" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R42" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S42" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T42" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U42" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V42" t="n">
-        <v>79.19191919191917</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="W42" t="n">
-        <v>79.19191919191917</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="X42" t="n">
-        <v>79.19191919191917</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Y42" t="n">
-        <v>79.19191919191917</v>
+        <v>118.3517937444931</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="C43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L43" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M43" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N43" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O43" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P43" t="n">
-        <v>133.6414398348344</v>
+        <v>130.4472581485427</v>
       </c>
       <c r="Q43" t="n">
-        <v>133.6414398348344</v>
+        <v>90.46354404567346</v>
       </c>
       <c r="R43" t="n">
-        <v>133.6414398348344</v>
+        <v>50.47982994280417</v>
       </c>
       <c r="S43" t="n">
-        <v>124.4121212121212</v>
+        <v>10.49611583993489</v>
       </c>
       <c r="T43" t="n">
-        <v>84.00808080808082</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="U43" t="n">
-        <v>84.00808080808082</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="V43" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="W43" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="X43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="Y43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
     </row>
     <row r="44">
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>220.0898510449805</v>
+        <v>224.6381464623686</v>
       </c>
       <c r="L17" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M17" t="n">
-        <v>230.3462332272727</v>
+        <v>234.7107591328471</v>
       </c>
       <c r="N17" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
-        <v>230.0982114216867</v>
+        <v>234.6465068390747</v>
       </c>
       <c r="P17" t="n">
-        <v>231.2329957552695</v>
+        <v>235.7812911726575</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9223,16 +9223,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>137.841438974359</v>
+        <v>142.389734391747</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>143.1026751972622</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339220183</v>
+        <v>146.6823293394063</v>
       </c>
       <c r="N18" t="n">
-        <v>131.3417120833333</v>
+        <v>135.7062379889076</v>
       </c>
       <c r="O18" t="n">
         <v>142.5962444444444</v>
@@ -9305,16 +9305,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L19" t="n">
-        <v>134.8846762812383</v>
+        <v>139.4329716986263</v>
       </c>
       <c r="M19" t="n">
-        <v>138.9257839476051</v>
+        <v>143.4740793649931</v>
       </c>
       <c r="N19" t="n">
-        <v>127.6855444652332</v>
+        <v>132.0500703708075</v>
       </c>
       <c r="O19" t="n">
-        <v>138.4565384518428</v>
+        <v>143.0048338692308</v>
       </c>
       <c r="P19" t="n">
         <v>135.0065633140411</v>
@@ -9381,13 +9381,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>260.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L20" t="n">
-        <v>274.1502533538256</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M20" t="n">
-        <v>270.3462332272727</v>
+        <v>272.6952875305729</v>
       </c>
       <c r="N20" t="n">
         <v>229.4130635965909</v>
@@ -9396,7 +9396,7 @@
         <v>230.0982114216867</v>
       </c>
       <c r="P20" t="n">
-        <v>271.2329957552695</v>
+        <v>275.3651681344982</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9460,25 +9460,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>177.841438974359</v>
+        <v>180.1904932776592</v>
       </c>
       <c r="L21" t="n">
-        <v>138.5543797798742</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M21" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N21" t="n">
-        <v>169.7255504671717</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>182.5962444444444</v>
+        <v>186.728416823673</v>
       </c>
       <c r="P21" t="n">
-        <v>173.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>184.1139464652501</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9548,7 +9548,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N22" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O22" t="n">
         <v>163.0416663658825</v>
@@ -9618,22 +9618,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>260.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L23" t="n">
-        <v>275.7664149699872</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M23" t="n">
-        <v>268.7300716111111</v>
+        <v>274.4784056065013</v>
       </c>
       <c r="N23" t="n">
-        <v>229.4130635965909</v>
+        <v>271.7621178998911</v>
       </c>
       <c r="O23" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P23" t="n">
-        <v>271.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q23" t="n">
         <v>212.3149906599047</v>
@@ -9700,22 +9700,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>138.5543797798742</v>
+        <v>180.9034340831744</v>
       </c>
       <c r="M24" t="n">
-        <v>142.1340339220183</v>
+        <v>186.2662063012469</v>
       </c>
       <c r="N24" t="n">
-        <v>169.7255504671717</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>182.5962444444444</v>
+        <v>186.728416823673</v>
       </c>
       <c r="P24" t="n">
-        <v>173.9744074143302</v>
+        <v>178.1065797935588</v>
       </c>
       <c r="Q24" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9785,7 +9785,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N25" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O25" t="n">
         <v>163.0416663658825</v>
@@ -9855,19 +9855,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>260.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L26" t="n">
-        <v>275.7664149699872</v>
+        <v>278.1154692732874</v>
       </c>
       <c r="M26" t="n">
-        <v>270.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N26" t="n">
-        <v>267.7969019804293</v>
+        <v>273.5452359758195</v>
       </c>
       <c r="O26" t="n">
-        <v>230.0982114216867</v>
+        <v>274.2303838009153</v>
       </c>
       <c r="P26" t="n">
         <v>231.2329957552695</v>
@@ -9934,22 +9934,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>177.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
-        <v>178.5543797798742</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>186.2662063012469</v>
       </c>
       <c r="N27" t="n">
-        <v>169.7255504671717</v>
+        <v>175.4738844625619</v>
       </c>
       <c r="O27" t="n">
-        <v>142.5962444444444</v>
+        <v>184.9452987477446</v>
       </c>
       <c r="P27" t="n">
-        <v>173.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
         <v>139.9817740860215</v>
@@ -10022,7 +10022,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N28" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O28" t="n">
         <v>163.0416663658825</v>
@@ -10092,22 +10092,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>220.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L29" t="n">
-        <v>235.7664149699872</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M29" t="n">
-        <v>270.3462332272727</v>
+        <v>272.6952875305729</v>
       </c>
       <c r="N29" t="n">
-        <v>269.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O29" t="n">
-        <v>270.0982114216868</v>
+        <v>274.2303838009153</v>
       </c>
       <c r="P29" t="n">
-        <v>269.6168341391079</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10171,25 +10171,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>177.841438974359</v>
+        <v>180.1904932776592</v>
       </c>
       <c r="L30" t="n">
-        <v>176.9382181637126</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>182.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444444</v>
+        <v>186.728416823673</v>
       </c>
       <c r="P30" t="n">
-        <v>133.9744074143302</v>
+        <v>178.1065797935588</v>
       </c>
       <c r="Q30" t="n">
-        <v>179.9817740860215</v>
+        <v>184.1139464652501</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10259,7 +10259,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N31" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O31" t="n">
         <v>163.0416663658825</v>
@@ -10329,22 +10329,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>220.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L32" t="n">
-        <v>274.1502533538256</v>
+        <v>278.1154692732874</v>
       </c>
       <c r="M32" t="n">
-        <v>270.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N32" t="n">
-        <v>269.4130635965909</v>
+        <v>273.5452359758195</v>
       </c>
       <c r="O32" t="n">
-        <v>270.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P32" t="n">
-        <v>231.2329957552695</v>
+        <v>275.3651681344982</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10411,19 +10411,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>176.9382181637126</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>182.1340339220183</v>
+        <v>186.2662063012469</v>
       </c>
       <c r="N33" t="n">
-        <v>171.3417120833333</v>
+        <v>175.4738844625619</v>
       </c>
       <c r="O33" t="n">
-        <v>182.5962444444444</v>
+        <v>186.728416823673</v>
       </c>
       <c r="P33" t="n">
-        <v>133.9744074143302</v>
+        <v>176.3234617176304</v>
       </c>
       <c r="Q33" t="n">
         <v>139.9817740860215</v>
@@ -10496,7 +10496,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N34" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O34" t="n">
         <v>163.0416663658825</v>
@@ -10566,22 +10566,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>220.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L35" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M35" t="n">
-        <v>268.7300716111112</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N35" t="n">
-        <v>269.4130635965909</v>
+        <v>271.7621178998911</v>
       </c>
       <c r="O35" t="n">
-        <v>270.0982114216868</v>
+        <v>274.2303838009153</v>
       </c>
       <c r="P35" t="n">
-        <v>271.2329957552695</v>
+        <v>275.3651681344982</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10645,25 +10645,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>181.9736113535876</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M36" t="n">
-        <v>142.1340339220183</v>
+        <v>186.2662063012469</v>
       </c>
       <c r="N36" t="n">
-        <v>171.3417120833333</v>
+        <v>173.6907663866335</v>
       </c>
       <c r="O36" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>173.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
-        <v>178.3656124698599</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10733,7 +10733,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N37" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O37" t="n">
         <v>163.0416663658825</v>
@@ -10803,19 +10803,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>220.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L38" t="n">
-        <v>275.7664149699872</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M38" t="n">
-        <v>270.3462332272727</v>
+        <v>272.6952875305729</v>
       </c>
       <c r="N38" t="n">
-        <v>267.7969019804293</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O38" t="n">
-        <v>270.0982114216868</v>
+        <v>274.2303838009153</v>
       </c>
       <c r="P38" t="n">
         <v>231.2329957552695</v>
@@ -10885,22 +10885,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>138.5543797798742</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M39" t="n">
-        <v>180.5178723058567</v>
+        <v>186.2662063012469</v>
       </c>
       <c r="N39" t="n">
-        <v>171.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>182.5962444444444</v>
+        <v>184.9452987477446</v>
       </c>
       <c r="P39" t="n">
-        <v>173.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>184.1139464652501</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10970,7 +10970,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N40" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O40" t="n">
         <v>163.0416663658825</v>
@@ -11040,22 +11040,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>258.4736894288189</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L41" t="n">
-        <v>275.7664149699872</v>
+        <v>275.3502919318278</v>
       </c>
       <c r="M41" t="n">
-        <v>230.3462332272727</v>
+        <v>269.9301101891133</v>
       </c>
       <c r="N41" t="n">
-        <v>229.4130635965909</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O41" t="n">
-        <v>270.0982114216868</v>
+        <v>268.0827398194126</v>
       </c>
       <c r="P41" t="n">
-        <v>271.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11119,10 +11119,10 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>177.841438974359</v>
+        <v>177.4253159361996</v>
       </c>
       <c r="L42" t="n">
-        <v>176.9382181637126</v>
+        <v>178.1382567417148</v>
       </c>
       <c r="M42" t="n">
         <v>142.1340339220183</v>
@@ -11134,10 +11134,10 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>173.9744074143302</v>
+        <v>171.9589358120561</v>
       </c>
       <c r="Q42" t="n">
-        <v>179.9817740860215</v>
+        <v>179.5656510478621</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11207,7 +11207,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N43" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O43" t="n">
         <v>163.0416663658825</v>
@@ -23704,16 +23704,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>415.302737515135</v>
+        <v>411.2965989114997</v>
       </c>
       <c r="H17" t="n">
-        <v>339.4748021157671</v>
+        <v>334.9265066983792</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>205.9275941530179</v>
       </c>
       <c r="J17" t="n">
-        <v>11.94928935461252</v>
+        <v>7.400993937224513</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23822,16 +23822,16 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>195.6164332774336</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9413820809748</v>
+        <v>221.3930866635868</v>
       </c>
       <c r="V18" t="n">
-        <v>232.8005871494253</v>
+        <v>228.2522917320373</v>
       </c>
       <c r="W18" t="n">
-        <v>251.6949831609196</v>
+        <v>247.6888445572843</v>
       </c>
       <c r="X18" t="n">
         <v>205.7729852034775</v>
@@ -23847,7 +23847,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>179.8319801819373</v>
+        <v>175.8258415783019</v>
       </c>
       <c r="C19" t="n">
         <v>167.2468210986278</v>
@@ -23898,10 +23898,10 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S19" t="n">
-        <v>224.0165980369723</v>
+        <v>219.4683026195843</v>
       </c>
       <c r="T19" t="n">
-        <v>227.9455894282815</v>
+        <v>223.3972940108935</v>
       </c>
       <c r="U19" t="n">
         <v>286.3190293564909</v>
@@ -23916,7 +23916,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y19" t="n">
-        <v>218.5846533520948</v>
+        <v>214.0363579347068</v>
       </c>
     </row>
     <row r="20">
@@ -23932,10 +23932,10 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D20" t="n">
-        <v>319.451041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
-        <v>341.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
         <v>406.8760457417114</v>
@@ -23974,19 +23974,19 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>149.8691179411497</v>
+        <v>105.7369455619211</v>
       </c>
       <c r="S20" t="n">
-        <v>209.0200695862453</v>
+        <v>164.8878972070167</v>
       </c>
       <c r="T20" t="n">
-        <v>183.0958495641314</v>
+        <v>178.9636771849028</v>
       </c>
       <c r="U20" t="n">
-        <v>251.3456529078365</v>
+        <v>212.474035476212</v>
       </c>
       <c r="V20" t="n">
-        <v>287.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
         <v>349.240968717413</v>
@@ -24005,28 +24005,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>122.4010112706387</v>
       </c>
       <c r="C21" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>103.3128931854102</v>
       </c>
       <c r="E21" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>105.0692123933839</v>
+        <v>106.1975949617593</v>
       </c>
       <c r="G21" t="n">
-        <v>97.34351716321063</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>72.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I21" t="n">
-        <v>54.16463285141511</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
         <v>0.7465913262578567</v>
@@ -24071,7 +24071,7 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
-        <v>205.7729852034775</v>
+        <v>161.6408128242489</v>
       </c>
       <c r="Y21" t="n">
         <v>205.6826957773044</v>
@@ -24087,7 +24087,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C22" t="n">
-        <v>127.2468210986278</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D22" t="n">
         <v>148.6154730182124</v>
@@ -24132,13 +24132,13 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>177.2933913771695</v>
+        <v>133.1612189979409</v>
       </c>
       <c r="S22" t="n">
-        <v>224.0165980369723</v>
+        <v>179.8844256577437</v>
       </c>
       <c r="T22" t="n">
-        <v>218.8085639917954</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U22" t="n">
         <v>286.3190293564909</v>
@@ -24147,13 +24147,13 @@
         <v>252.137643323828</v>
       </c>
       <c r="W22" t="n">
-        <v>246.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X22" t="n">
-        <v>225.7096553890372</v>
+        <v>181.5774830098086</v>
       </c>
       <c r="Y22" t="n">
-        <v>178.5846533520948</v>
+        <v>217.7942029044125</v>
       </c>
     </row>
     <row r="23">
@@ -24166,25 +24166,25 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
-        <v>325.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
-        <v>314.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
-        <v>406.8760457417114</v>
+        <v>362.7438733624829</v>
       </c>
       <c r="G23" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
-        <v>339.4748021157671</v>
+        <v>295.3426297365386</v>
       </c>
       <c r="I23" t="n">
-        <v>170.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -24214,7 +24214,7 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S23" t="n">
-        <v>173.7880695862454</v>
+        <v>170.1484521546208</v>
       </c>
       <c r="T23" t="n">
         <v>223.0958495641314</v>
@@ -24232,7 +24232,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
-        <v>386.2379386560536</v>
+        <v>342.105766276825</v>
       </c>
     </row>
     <row r="24">
@@ -24245,19 +24245,19 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>128.5763266090871</v>
       </c>
       <c r="D24" t="n">
-        <v>112.2130655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>117.6450804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
-        <v>105.0692123933839</v>
+        <v>100.9370400141553</v>
       </c>
       <c r="G24" t="n">
-        <v>97.34351716321063</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
         <v>112.2354442364965</v>
@@ -24290,10 +24290,10 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>100.1578341526431</v>
+        <v>56.02566177341454</v>
       </c>
       <c r="S24" t="n">
-        <v>171.6831711038378</v>
+        <v>132.8115536722133</v>
       </c>
       <c r="T24" t="n">
         <v>200.1647286948216</v>
@@ -24324,7 +24324,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C25" t="n">
-        <v>167.2468210986278</v>
+        <v>166.4563706509456</v>
       </c>
       <c r="D25" t="n">
         <v>148.6154730182124</v>
@@ -24339,13 +24339,13 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H25" t="n">
-        <v>122.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I25" t="n">
-        <v>115.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J25" t="n">
-        <v>84.22215468018669</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K25" t="n">
         <v>22.26949182588285</v>
@@ -24381,16 +24381,16 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V25" t="n">
-        <v>212.137643323828</v>
+        <v>208.0054709445994</v>
       </c>
       <c r="W25" t="n">
         <v>286.522998336591</v>
       </c>
       <c r="X25" t="n">
-        <v>225.7096553890372</v>
+        <v>181.5774830098086</v>
       </c>
       <c r="Y25" t="n">
-        <v>218.5846533520948</v>
+        <v>174.4524809728662</v>
       </c>
     </row>
     <row r="26">
@@ -24448,25 +24448,25 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>110.9975005095251</v>
       </c>
       <c r="S26" t="n">
-        <v>209.0200695862453</v>
+        <v>164.8878972070167</v>
       </c>
       <c r="T26" t="n">
-        <v>223.0958495641314</v>
+        <v>178.9636771849028</v>
       </c>
       <c r="U26" t="n">
-        <v>216.1136529078365</v>
+        <v>207.2134805286079</v>
       </c>
       <c r="V26" t="n">
-        <v>287.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
-        <v>309.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
-        <v>329.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
         <v>386.2379386560536</v>
@@ -24497,7 +24497,7 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
-        <v>112.2354442364965</v>
+        <v>73.36382680487192</v>
       </c>
       <c r="I27" t="n">
         <v>89.39663285141508</v>
@@ -24536,19 +24536,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>190.7093820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>192.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>211.6949831609196</v>
+        <v>207.562810781691</v>
       </c>
       <c r="X27" t="n">
-        <v>165.7729852034775</v>
+        <v>161.6408128242489</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>161.5505233980758</v>
       </c>
     </row>
     <row r="28">
@@ -24561,7 +24561,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C28" t="n">
-        <v>127.2468210986278</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D28" t="n">
         <v>148.6154730182124</v>
@@ -24579,13 +24579,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I28" t="n">
-        <v>155.4504749272583</v>
+        <v>111.3183025480297</v>
       </c>
       <c r="J28" t="n">
-        <v>93.35918011667277</v>
+        <v>70.70604911564477</v>
       </c>
       <c r="K28" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -24609,13 +24609,13 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S28" t="n">
-        <v>214.8795726004862</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T28" t="n">
-        <v>187.9455894282815</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U28" t="n">
-        <v>246.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24627,7 +24627,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y28" t="n">
-        <v>218.5846533520948</v>
+        <v>174.4524809728662</v>
       </c>
     </row>
     <row r="29">
@@ -24640,16 +24640,16 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C29" t="n">
-        <v>365.2728917710076</v>
+        <v>321.1407193917789</v>
       </c>
       <c r="D29" t="n">
-        <v>329.4417408352278</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>366.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
         <v>415.302737515135</v>
@@ -24682,7 +24682,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
         <v>149.8691179411497</v>
@@ -24691,22 +24691,22 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>223.0958495641314</v>
+        <v>178.9636771849028</v>
       </c>
       <c r="U29" t="n">
-        <v>251.3456529078365</v>
+        <v>207.2134805286079</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
-        <v>349.240968717413</v>
+        <v>310.3693512857885</v>
       </c>
       <c r="X29" t="n">
-        <v>329.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>346.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="30">
@@ -24716,10 +24716,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>122.4010112706387</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>128.5763266090871</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
@@ -24764,10 +24764,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>64.92583415264315</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>171.6831711038378</v>
+        <v>127.5509987246092</v>
       </c>
       <c r="T30" t="n">
         <v>200.1647286948216</v>
@@ -24776,16 +24776,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>192.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X30" t="n">
-        <v>165.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>166.8110783456798</v>
       </c>
     </row>
     <row r="31">
@@ -24795,16 +24795,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>179.8319801819373</v>
+        <v>135.6998078027087</v>
       </c>
       <c r="C31" t="n">
-        <v>127.2468210986278</v>
+        <v>166.4563706509456</v>
       </c>
       <c r="D31" t="n">
-        <v>108.6154730182124</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E31" t="n">
-        <v>137.2969372100831</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F31" t="n">
         <v>145.4210480229312</v>
@@ -24846,7 +24846,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S31" t="n">
-        <v>184.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T31" t="n">
         <v>227.9455894282815</v>
@@ -24858,13 +24858,13 @@
         <v>252.137643323828</v>
       </c>
       <c r="W31" t="n">
-        <v>286.522998336591</v>
+        <v>242.3908259573624</v>
       </c>
       <c r="X31" t="n">
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>218.5846533520948</v>
+        <v>174.4524809728662</v>
       </c>
     </row>
     <row r="32">
@@ -24877,16 +24877,16 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
-        <v>325.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D32" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>341.9303700722618</v>
+        <v>337.7981976930332</v>
       </c>
       <c r="F32" t="n">
-        <v>371.6440457417115</v>
+        <v>368.0044283100869</v>
       </c>
       <c r="G32" t="n">
         <v>415.302737515135</v>
@@ -24922,10 +24922,10 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>149.8691179411497</v>
+        <v>105.7369455619211</v>
       </c>
       <c r="S32" t="n">
-        <v>209.0200695862453</v>
+        <v>164.8878972070167</v>
       </c>
       <c r="T32" t="n">
         <v>223.0958495641314</v>
@@ -24940,7 +24940,7 @@
         <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
-        <v>329.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
         <v>386.2379386560536</v>
@@ -24956,28 +24956,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>172.7084989883157</v>
+        <v>128.5763266090871</v>
       </c>
       <c r="D33" t="n">
-        <v>147.4450655646388</v>
+        <v>108.5734481330142</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>113.5129080761724</v>
       </c>
       <c r="F33" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>102.8581084894685</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>72.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25001,7 +25001,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>60.15783415264313</v>
+        <v>56.02566177341454</v>
       </c>
       <c r="S33" t="n">
         <v>171.6831711038378</v>
@@ -25016,7 +25016,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
@@ -25035,7 +25035,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C34" t="n">
-        <v>127.2468210986278</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D34" t="n">
         <v>148.6154730182124</v>
@@ -25047,10 +25047,10 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>127.9909793584588</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H34" t="n">
-        <v>153.0901470709535</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I34" t="n">
         <v>155.4504749272583</v>
@@ -25083,25 +25083,25 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S34" t="n">
-        <v>224.0165980369723</v>
+        <v>179.8844256577437</v>
       </c>
       <c r="T34" t="n">
-        <v>227.9455894282815</v>
+        <v>183.8134170490529</v>
       </c>
       <c r="U34" t="n">
         <v>286.3190293564909</v>
       </c>
       <c r="V34" t="n">
-        <v>212.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
         <v>286.522998336591</v>
       </c>
       <c r="X34" t="n">
-        <v>225.7096553890372</v>
+        <v>224.9192049413549</v>
       </c>
       <c r="Y34" t="n">
-        <v>218.5846533520948</v>
+        <v>174.4524809728662</v>
       </c>
     </row>
     <row r="35">
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>342.7338416634806</v>
+        <v>338.601669284252</v>
       </c>
       <c r="C35" t="n">
-        <v>325.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
@@ -25159,19 +25159,19 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>109.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
-        <v>173.7880695862454</v>
+        <v>164.8878972070167</v>
       </c>
       <c r="T35" t="n">
-        <v>223.0958495641314</v>
+        <v>178.9636771849028</v>
       </c>
       <c r="U35" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>327.7522584701349</v>
+        <v>288.8806410385104</v>
       </c>
       <c r="W35" t="n">
         <v>349.240968717413</v>
@@ -25190,13 +25190,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>122.4010112706387</v>
       </c>
       <c r="C36" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>147.4450655646388</v>
+        <v>108.5734481330142</v>
       </c>
       <c r="E36" t="n">
         <v>157.6450804554009</v>
@@ -25241,25 +25241,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>136.4511711038379</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>185.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>192.8005871494253</v>
+        <v>188.6684147701967</v>
       </c>
       <c r="W36" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X36" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
-        <v>205.6826957773044</v>
+        <v>161.5505233980758</v>
       </c>
     </row>
     <row r="37">
@@ -25272,13 +25272,13 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C37" t="n">
-        <v>167.2468210986278</v>
+        <v>123.1146487193992</v>
       </c>
       <c r="D37" t="n">
-        <v>108.6154730182124</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E37" t="n">
-        <v>106.4339626465692</v>
+        <v>102.3017902673406</v>
       </c>
       <c r="F37" t="n">
         <v>145.4210480229312</v>
@@ -25311,7 +25311,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.721440735106512</v>
+        <v>1.930990287424243</v>
       </c>
       <c r="Q37" t="n">
         <v>86.16204325169439</v>
@@ -25329,16 +25329,16 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V37" t="n">
-        <v>212.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W37" t="n">
         <v>286.522998336591</v>
       </c>
       <c r="X37" t="n">
-        <v>216.5726299525511</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y37" t="n">
-        <v>218.5846533520948</v>
+        <v>174.4524809728662</v>
       </c>
     </row>
     <row r="38">
@@ -25372,7 +25372,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25396,19 +25396,19 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>114.6371179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>169.0200695862453</v>
+        <v>182.0977415092333</v>
       </c>
       <c r="T38" t="n">
-        <v>183.0958495641314</v>
+        <v>178.9636771849028</v>
       </c>
       <c r="U38" t="n">
-        <v>211.3456529078365</v>
+        <v>207.2134805286079</v>
       </c>
       <c r="V38" t="n">
-        <v>327.7522584701349</v>
+        <v>283.6200860909063</v>
       </c>
       <c r="W38" t="n">
         <v>349.240968717413</v>
@@ -25436,13 +25436,13 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>157.6450804554009</v>
+        <v>118.7734630237764</v>
       </c>
       <c r="F39" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>97.34351716321063</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
         <v>112.2354442364965</v>
@@ -25481,22 +25481,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>156.032556315593</v>
       </c>
       <c r="U39" t="n">
-        <v>185.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>211.6949831609196</v>
+        <v>207.562810781691</v>
       </c>
       <c r="X39" t="n">
-        <v>205.7729852034775</v>
+        <v>161.6408128242489</v>
       </c>
       <c r="Y39" t="n">
-        <v>170.4506957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -25512,7 +25512,7 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D40" t="n">
-        <v>108.6154730182124</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E40" t="n">
         <v>146.4339626465692</v>
@@ -25548,28 +25548,28 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>86.16204325169439</v>
+        <v>42.02987087246579</v>
       </c>
       <c r="R40" t="n">
-        <v>177.2933913771695</v>
+        <v>133.1612189979409</v>
       </c>
       <c r="S40" t="n">
-        <v>214.8795726004862</v>
+        <v>181.8154159451679</v>
       </c>
       <c r="T40" t="n">
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>246.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W40" t="n">
-        <v>246.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X40" t="n">
         <v>225.7096553890372</v>
@@ -25588,13 +25588,13 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C41" t="n">
-        <v>365.2728917710076</v>
+        <v>325.689014809167</v>
       </c>
       <c r="D41" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>381.9303700722618</v>
+        <v>342.3464931104212</v>
       </c>
       <c r="F41" t="n">
         <v>406.8760457417114</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25645,16 +25645,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>287.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>309.240968717413</v>
+        <v>324.3661891039686</v>
       </c>
       <c r="X41" t="n">
-        <v>329.731100678469</v>
+        <v>330.1472237166284</v>
       </c>
       <c r="Y41" t="n">
-        <v>351.0059386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="42">
@@ -25667,10 +25667,10 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>132.7084989883157</v>
+        <v>138.5896114865844</v>
       </c>
       <c r="D42" t="n">
-        <v>112.2130655646388</v>
+        <v>107.8611886027982</v>
       </c>
       <c r="E42" t="n">
         <v>157.6450804554009</v>
@@ -25682,13 +25682,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>72.65156727465587</v>
       </c>
       <c r="I42" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25721,10 +25721,10 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>185.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>192.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
         <v>251.6949831609196</v>
@@ -25733,7 +25733,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>166.0988188154638</v>
       </c>
     </row>
     <row r="43">
@@ -25785,31 +25785,31 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>86.16204325169439</v>
+        <v>46.5781662898538</v>
       </c>
       <c r="R43" t="n">
-        <v>177.2933913771695</v>
+        <v>137.7095144153289</v>
       </c>
       <c r="S43" t="n">
-        <v>214.8795726004862</v>
+        <v>184.4327210751317</v>
       </c>
       <c r="T43" t="n">
-        <v>187.9455894282815</v>
+        <v>220.6894778021237</v>
       </c>
       <c r="U43" t="n">
         <v>286.3190293564909</v>
       </c>
       <c r="V43" t="n">
-        <v>212.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W43" t="n">
         <v>286.522998336591</v>
       </c>
       <c r="X43" t="n">
-        <v>185.7096553890372</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y43" t="n">
         <v>218.5846533520948</v>
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333272.9571474838</v>
+        <v>337268.6921860034</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>367442.4120036121</v>
+        <v>370626.5453121332</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>367442.412003612</v>
+        <v>370626.545312133</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>367442.4120036121</v>
+        <v>370626.5453121332</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>367442.412003612</v>
+        <v>370626.5453121331</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>367442.4120036121</v>
+        <v>370626.5453121332</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>367442.4120036119</v>
+        <v>370626.545312133</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>367442.412003612</v>
+        <v>370626.5453121333</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>367442.412003612</v>
+        <v>367121.7595465879</v>
       </c>
     </row>
     <row r="16">
@@ -26261,46 +26261,46 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>48378.33248915088</v>
+      </c>
+      <c r="C2" t="n">
         <v>48378.33248915087</v>
       </c>
-      <c r="C2" t="n">
-        <v>48378.33248915088</v>
-      </c>
       <c r="D2" t="n">
-        <v>48378.33248915088</v>
+        <v>48378.33248915087</v>
       </c>
       <c r="E2" t="n">
-        <v>48378.33248915088</v>
+        <v>48378.33248915087</v>
       </c>
       <c r="F2" t="n">
         <v>48378.33248915088</v>
       </c>
       <c r="G2" t="n">
-        <v>48378.33248915088</v>
+        <v>48958.16865566389</v>
       </c>
       <c r="H2" t="n">
-        <v>53336.79082650791</v>
+        <v>53798.85240803943</v>
       </c>
       <c r="I2" t="n">
-        <v>53336.79082650792</v>
+        <v>53798.85240803942</v>
       </c>
       <c r="J2" t="n">
-        <v>53336.79082650791</v>
+        <v>53798.85240803943</v>
       </c>
       <c r="K2" t="n">
-        <v>53336.7908265079</v>
+        <v>53798.85240803945</v>
       </c>
       <c r="L2" t="n">
-        <v>53336.79082650792</v>
+        <v>53798.85240803943</v>
       </c>
       <c r="M2" t="n">
-        <v>53336.79082650789</v>
+        <v>53798.85240803943</v>
       </c>
       <c r="N2" t="n">
-        <v>53336.7908265079</v>
+        <v>53798.85240803943</v>
       </c>
       <c r="O2" t="n">
-        <v>53336.7908265079</v>
+        <v>53290.25974031941</v>
       </c>
       <c r="P2" t="n">
         <v>48378.33248915088</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1246.619549474791</v>
       </c>
       <c r="H3" t="n">
-        <v>10792.36</v>
+        <v>10680.08625919725</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5375.37027657232</v>
+        <v>4199.508028572124</v>
       </c>
       <c r="C4" t="n">
-        <v>5375.37027657232</v>
+        <v>4199.508028572124</v>
       </c>
       <c r="D4" t="n">
-        <v>5375.37027657232</v>
+        <v>4199.508028572124</v>
       </c>
       <c r="E4" t="n">
-        <v>5375.37027657232</v>
+        <v>4199.508028572124</v>
       </c>
       <c r="F4" t="n">
-        <v>5375.37027657232</v>
+        <v>4199.508028572124</v>
       </c>
       <c r="G4" t="n">
-        <v>5375.37027657232</v>
+        <v>4254.80705419072</v>
       </c>
       <c r="H4" t="n">
-        <v>5971.22396923389</v>
+        <v>4716.463484564711</v>
       </c>
       <c r="I4" t="n">
-        <v>5971.22396923389</v>
+        <v>4716.463484564711</v>
       </c>
       <c r="J4" t="n">
-        <v>5971.22396923389</v>
+        <v>4716.463484564711</v>
       </c>
       <c r="K4" t="n">
-        <v>5971.22396923389</v>
+        <v>4716.463484564711</v>
       </c>
       <c r="L4" t="n">
-        <v>5971.22396923389</v>
+        <v>4716.463484564711</v>
       </c>
       <c r="M4" t="n">
-        <v>5971.22396923389</v>
+        <v>4716.463484564711</v>
       </c>
       <c r="N4" t="n">
-        <v>5971.22396923389</v>
+        <v>4716.463484564711</v>
       </c>
       <c r="O4" t="n">
-        <v>5971.22396923389</v>
+        <v>4667.958957620807</v>
       </c>
       <c r="P4" t="n">
-        <v>5375.37027657232</v>
+        <v>4199.508028572124</v>
       </c>
     </row>
     <row r="5">
@@ -26432,31 +26432,31 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>276.5363613771906</v>
       </c>
       <c r="H5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="I5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="J5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="K5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="L5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="M5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="N5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="O5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9375.362212578555</v>
+        <v>10551.22446057876</v>
       </c>
       <c r="C6" t="n">
-        <v>9375.362212578562</v>
+        <v>10551.22446057875</v>
       </c>
       <c r="D6" t="n">
-        <v>9375.362212578562</v>
+        <v>10551.22446057875</v>
       </c>
       <c r="E6" t="n">
-        <v>43002.96221257856</v>
+        <v>44178.82446057875</v>
       </c>
       <c r="F6" t="n">
-        <v>43002.96221257856</v>
+        <v>44178.82446057875</v>
       </c>
       <c r="G6" t="n">
-        <v>43002.96221257856</v>
+        <v>43180.20569062119</v>
       </c>
       <c r="H6" t="n">
-        <v>34141.20685727402</v>
+        <v>35719.06658362037</v>
       </c>
       <c r="I6" t="n">
-        <v>44933.56685727403</v>
+        <v>46399.15284281761</v>
       </c>
       <c r="J6" t="n">
-        <v>44933.56685727402</v>
+        <v>46399.15284281762</v>
       </c>
       <c r="K6" t="n">
-        <v>44933.56685727401</v>
+        <v>46399.15284281764</v>
       </c>
       <c r="L6" t="n">
-        <v>44933.56685727403</v>
+        <v>46399.15284281762</v>
       </c>
       <c r="M6" t="n">
-        <v>44933.566857274</v>
+        <v>46399.15284281762</v>
       </c>
       <c r="N6" t="n">
-        <v>44933.56685727401</v>
+        <v>46399.15284281762</v>
       </c>
       <c r="O6" t="n">
-        <v>44933.56685727401</v>
+        <v>46215.60106341869</v>
       </c>
       <c r="P6" t="n">
-        <v>43002.96221257856</v>
+        <v>44178.82446057875</v>
       </c>
     </row>
   </sheetData>
@@ -26742,31 +26742,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="I4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="J4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,13 +26892,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26907,16 +26907,16 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26925,16 +26925,16 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,7 +26947,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -26956,37 +26956,37 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="P4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
   </sheetData>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.36452590557435</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35878,16 +35878,16 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.36452590557435</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -35960,16 +35960,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.36452590557435</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -36036,13 +36036,13 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L20" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M20" t="n">
-        <v>40</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -36051,7 +36051,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36115,25 +36115,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36203,7 +36203,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N22" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O22" t="n">
         <v>24.58512791403967</v>
@@ -36273,22 +36273,22 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L23" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M23" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>42.34905430330016</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36355,22 +36355,22 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N24" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P24" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36440,7 +36440,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N25" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O25" t="n">
         <v>24.58512791403967</v>
@@ -36510,19 +36510,19 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L26" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="M26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -36589,22 +36589,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N27" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>42.34905430330016</v>
       </c>
       <c r="P27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36677,7 +36677,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O28" t="n">
         <v>24.58512791403967</v>
@@ -36747,22 +36747,22 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M29" t="n">
-        <v>40</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="N29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P29" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36826,25 +36826,25 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="L30" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q30" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36914,7 +36914,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N31" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O31" t="n">
         <v>24.58512791403967</v>
@@ -36984,22 +36984,22 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L32" t="n">
-        <v>38.38383838383839</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="M32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37066,19 +37066,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N33" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O33" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>42.34905430330016</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37151,7 +37151,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N34" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O34" t="n">
         <v>24.58512791403967</v>
@@ -37221,22 +37221,22 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="O35" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P35" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37300,25 +37300,25 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N36" t="n">
-        <v>40</v>
+        <v>42.34905430330016</v>
       </c>
       <c r="O36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37388,7 +37388,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N37" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O37" t="n">
         <v>24.58512791403967</v>
@@ -37458,19 +37458,19 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L38" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M38" t="n">
-        <v>40</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="N38" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37540,22 +37540,22 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M39" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>40</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="P39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37625,7 +37625,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N40" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O40" t="n">
         <v>24.58512791403967</v>
@@ -37695,22 +37695,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O41" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="P41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37774,10 +37774,10 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="L42" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -37789,10 +37789,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="Q42" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37862,7 +37862,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N43" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O43" t="n">
         <v>24.58512791403967</v>
